--- a/storage/app/private/CLIENTES/YENNIFER/Bitacora_YENNIFER_JUNIO-2026.xlsx
+++ b/storage/app/private/CLIENTES/YENNIFER/Bitacora_YENNIFER_JUNIO-2026.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="16">
   <si>
     <t>Facturas De Yennifer</t>
   </si>
@@ -61,6 +61,9 @@
   </si>
   <si>
     <t>MONTO</t>
+  </si>
+  <si>
+    <t>prueba</t>
   </si>
 </sst>
 </file>
@@ -583,7 +586,7 @@
   <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="59.7" bestFit="true" customWidth="true" style="0"/>
+    <col min="1" max="1" width="45.846" bestFit="true" customWidth="true" style="0"/>
     <col min="2" max="2" width="13.997" bestFit="true" customWidth="true" style="0"/>
     <col min="3" max="3" width="9.283" bestFit="true" customWidth="true" style="0"/>
     <col min="4" max="4" width="9.283" bestFit="true" customWidth="true" style="0"/>
@@ -591,14 +594,29 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>11</v>
       </c>
+      <c r="B1"/>
+      <c r="C1"/>
+      <c r="D1"/>
+      <c r="E1"/>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="2" t="s">
+      <c r="A2" t="s">
         <v>1</v>
       </c>
+      <c r="B2"/>
+      <c r="C2"/>
+      <c r="D2"/>
+      <c r="E2"/>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3"/>
+      <c r="B3"/>
+      <c r="C3"/>
+      <c r="D3"/>
+      <c r="E3"/>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="3" t="s">
@@ -621,7 +639,9 @@
       <c r="A5" s="5">
         <v>1</v>
       </c>
-      <c r="B5" s="6"/>
+      <c r="B5" s="6" t="s">
+        <v>15</v>
+      </c>
       <c r="C5" s="5"/>
       <c r="D5" s="7"/>
       <c r="E5" s="6"/>
@@ -672,6 +692,8 @@
       <c r="E10" s="11"/>
     </row>
     <row r="11" spans="1:5">
+      <c r="A11"/>
+      <c r="B11"/>
       <c r="C11" s="8" t="s">
         <v>10</v>
       </c>
@@ -679,6 +701,7 @@
         <f>SUM(D5:D10)</f>
         <v>0</v>
       </c>
+      <c r="E11"/>
     </row>
   </sheetData>
   <printOptions gridLines="false" gridLinesSet="true"/>
